--- a/artfynd/A 58967-2024 artfynd.xlsx
+++ b/artfynd/A 58967-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121631202</v>
+        <v>121631195</v>
       </c>
       <c r="B2" t="n">
-        <v>56250</v>
+        <v>56258</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121631195</v>
+        <v>121631202</v>
       </c>
       <c r="B3" t="n">
-        <v>56257</v>
+        <v>56251</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -910,7 +910,7 @@
         <v>121631174</v>
       </c>
       <c r="B4" t="n">
-        <v>56271</v>
+        <v>56272</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 58967-2024 artfynd.xlsx
+++ b/artfynd/A 58967-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121631195</v>
+        <v>121631174</v>
       </c>
       <c r="B2" t="n">
-        <v>56258</v>
+        <v>56272</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205992</v>
+        <v>206002</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121631174</v>
+        <v>121631202</v>
       </c>
       <c r="B3" t="n">
-        <v>56272</v>
+        <v>56251</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121631202</v>
+        <v>121631195</v>
       </c>
       <c r="B4" t="n">
-        <v>56251</v>
+        <v>56258</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>

--- a/artfynd/A 58967-2024 artfynd.xlsx
+++ b/artfynd/A 58967-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121631174</v>
+        <v>121631202</v>
       </c>
       <c r="B2" t="n">
-        <v>56272</v>
+        <v>56251</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121631202</v>
+        <v>121631195</v>
       </c>
       <c r="B3" t="n">
-        <v>56251</v>
+        <v>56258</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121631195</v>
+        <v>121631174</v>
       </c>
       <c r="B4" t="n">
-        <v>56258</v>
+        <v>56272</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205992</v>
+        <v>206002</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>

--- a/artfynd/A 58967-2024 artfynd.xlsx
+++ b/artfynd/A 58967-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121631202</v>
+        <v>121631195</v>
       </c>
       <c r="B2" t="n">
-        <v>56251</v>
+        <v>56258</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121631195</v>
+        <v>121631202</v>
       </c>
       <c r="B3" t="n">
-        <v>56258</v>
+        <v>56251</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>

--- a/artfynd/A 58967-2024 artfynd.xlsx
+++ b/artfynd/A 58967-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121631195</v>
+        <v>121631202</v>
       </c>
       <c r="B2" t="n">
-        <v>56258</v>
+        <v>56251</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121631202</v>
+        <v>121631195</v>
       </c>
       <c r="B3" t="n">
-        <v>56251</v>
+        <v>56258</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
